--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934433</v>
+        <v>119934431</v>
       </c>
       <c r="B2" t="n">
         <v>91834</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727372</v>
+        <v>727364</v>
       </c>
       <c r="R2" t="n">
-        <v>7214503</v>
+        <v>7214523</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934431</v>
+        <v>119934146</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727364</v>
+        <v>727338</v>
       </c>
       <c r="R3" t="n">
-        <v>7214523</v>
+        <v>7214647</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934231</v>
+        <v>119934147</v>
       </c>
       <c r="B4" t="n">
-        <v>89252</v>
+        <v>96868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727355</v>
+        <v>727372</v>
       </c>
       <c r="R4" t="n">
-        <v>7214538</v>
+        <v>7214502</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934344</v>
+        <v>119934345</v>
       </c>
       <c r="B5" t="n">
         <v>91840</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727339</v>
+        <v>727354</v>
       </c>
       <c r="R5" t="n">
-        <v>7214582</v>
+        <v>7214484</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934345</v>
+        <v>119934344</v>
       </c>
       <c r="B6" t="n">
         <v>91840</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727354</v>
+        <v>727339</v>
       </c>
       <c r="R6" t="n">
-        <v>7214484</v>
+        <v>7214582</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934147</v>
+        <v>119934231</v>
       </c>
       <c r="B7" t="n">
-        <v>96868</v>
+        <v>89252</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727372</v>
+        <v>727355</v>
       </c>
       <c r="R7" t="n">
-        <v>7214502</v>
+        <v>7214538</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934146</v>
+        <v>119934433</v>
       </c>
       <c r="B8" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727338</v>
+        <v>727372</v>
       </c>
       <c r="R8" t="n">
-        <v>7214647</v>
+        <v>7214503</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934431</v>
+        <v>119934146</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727364</v>
+        <v>727338</v>
       </c>
       <c r="R2" t="n">
-        <v>7214523</v>
+        <v>7214647</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934146</v>
+        <v>119934433</v>
       </c>
       <c r="B3" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727338</v>
+        <v>727372</v>
       </c>
       <c r="R3" t="n">
-        <v>7214647</v>
+        <v>7214503</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934147</v>
+        <v>119934231</v>
       </c>
       <c r="B4" t="n">
-        <v>96868</v>
+        <v>89252</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727372</v>
+        <v>727355</v>
       </c>
       <c r="R4" t="n">
-        <v>7214502</v>
+        <v>7214538</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934345</v>
+        <v>119934147</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727354</v>
+        <v>727372</v>
       </c>
       <c r="R5" t="n">
-        <v>7214484</v>
+        <v>7214502</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934344</v>
+        <v>119934345</v>
       </c>
       <c r="B6" t="n">
         <v>91840</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727339</v>
+        <v>727354</v>
       </c>
       <c r="R6" t="n">
-        <v>7214582</v>
+        <v>7214484</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934231</v>
+        <v>119934344</v>
       </c>
       <c r="B7" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727355</v>
+        <v>727339</v>
       </c>
       <c r="R7" t="n">
-        <v>7214538</v>
+        <v>7214582</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934433</v>
+        <v>119934431</v>
       </c>
       <c r="B8" t="n">
         <v>91834</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727372</v>
+        <v>727364</v>
       </c>
       <c r="R8" t="n">
-        <v>7214503</v>
+        <v>7214523</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934146</v>
+        <v>119934231</v>
       </c>
       <c r="B2" t="n">
-        <v>96868</v>
+        <v>89252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727338</v>
+        <v>727355</v>
       </c>
       <c r="R2" t="n">
-        <v>7214647</v>
+        <v>7214538</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934433</v>
+        <v>119934146</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727372</v>
+        <v>727338</v>
       </c>
       <c r="R3" t="n">
-        <v>7214503</v>
+        <v>7214647</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934231</v>
+        <v>119934345</v>
       </c>
       <c r="B4" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727355</v>
+        <v>727354</v>
       </c>
       <c r="R4" t="n">
-        <v>7214538</v>
+        <v>7214484</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934147</v>
+        <v>119934344</v>
       </c>
       <c r="B5" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727372</v>
+        <v>727339</v>
       </c>
       <c r="R5" t="n">
-        <v>7214502</v>
+        <v>7214582</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934345</v>
+        <v>119934431</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727354</v>
+        <v>727364</v>
       </c>
       <c r="R6" t="n">
-        <v>7214484</v>
+        <v>7214523</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934344</v>
+        <v>119934433</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727339</v>
+        <v>727372</v>
       </c>
       <c r="R7" t="n">
-        <v>7214582</v>
+        <v>7214503</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934431</v>
+        <v>119934147</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727364</v>
+        <v>727372</v>
       </c>
       <c r="R8" t="n">
-        <v>7214523</v>
+        <v>7214502</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934146</v>
+        <v>119934345</v>
       </c>
       <c r="B3" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727338</v>
+        <v>727354</v>
       </c>
       <c r="R3" t="n">
-        <v>7214647</v>
+        <v>7214484</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934345</v>
+        <v>119934146</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727354</v>
+        <v>727338</v>
       </c>
       <c r="R4" t="n">
-        <v>7214484</v>
+        <v>7214647</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934345</v>
+        <v>119934146</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727354</v>
+        <v>727338</v>
       </c>
       <c r="R3" t="n">
-        <v>7214484</v>
+        <v>7214647</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934146</v>
+        <v>119934345</v>
       </c>
       <c r="B4" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727338</v>
+        <v>727354</v>
       </c>
       <c r="R4" t="n">
-        <v>7214647</v>
+        <v>7214484</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934231</v>
+        <v>119934146</v>
       </c>
       <c r="B2" t="n">
-        <v>89252</v>
+        <v>96891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727355</v>
+        <v>727338</v>
       </c>
       <c r="R2" t="n">
-        <v>7214538</v>
+        <v>7214647</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934146</v>
+        <v>119934231</v>
       </c>
       <c r="B3" t="n">
-        <v>96868</v>
+        <v>89269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727338</v>
+        <v>727355</v>
       </c>
       <c r="R3" t="n">
-        <v>7214647</v>
+        <v>7214538</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>119934345</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>119934344</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934431</v>
+        <v>119934147</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>96891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727364</v>
+        <v>727372</v>
       </c>
       <c r="R6" t="n">
-        <v>7214523</v>
+        <v>7214502</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,7 +1238,7 @@
         <v>119934433</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934147</v>
+        <v>119934431</v>
       </c>
       <c r="B8" t="n">
-        <v>96868</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727372</v>
+        <v>727364</v>
       </c>
       <c r="R8" t="n">
-        <v>7214502</v>
+        <v>7214523</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934231</v>
+        <v>119934345</v>
       </c>
       <c r="B3" t="n">
-        <v>89269</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727355</v>
+        <v>727354</v>
       </c>
       <c r="R3" t="n">
-        <v>7214538</v>
+        <v>7214484</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934345</v>
+        <v>119934344</v>
       </c>
       <c r="B4" t="n">
         <v>91858</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727354</v>
+        <v>727339</v>
       </c>
       <c r="R4" t="n">
-        <v>7214484</v>
+        <v>7214582</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934344</v>
+        <v>119934433</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727339</v>
+        <v>727372</v>
       </c>
       <c r="R5" t="n">
-        <v>7214582</v>
+        <v>7214503</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934433</v>
+        <v>119934431</v>
       </c>
       <c r="B7" t="n">
         <v>91852</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727372</v>
+        <v>727364</v>
       </c>
       <c r="R7" t="n">
-        <v>7214503</v>
+        <v>7214523</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934431</v>
+        <v>119934231</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727364</v>
+        <v>727355</v>
       </c>
       <c r="R8" t="n">
-        <v>7214523</v>
+        <v>7214538</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934146</v>
+        <v>119934231</v>
       </c>
       <c r="B2" t="n">
-        <v>96891</v>
+        <v>89269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727338</v>
+        <v>727355</v>
       </c>
       <c r="R2" t="n">
-        <v>7214647</v>
+        <v>7214538</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934345</v>
+        <v>119934344</v>
       </c>
       <c r="B3" t="n">
         <v>91858</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727354</v>
+        <v>727339</v>
       </c>
       <c r="R3" t="n">
-        <v>7214484</v>
+        <v>7214582</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934344</v>
+        <v>119934431</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727339</v>
+        <v>727364</v>
       </c>
       <c r="R4" t="n">
-        <v>7214582</v>
+        <v>7214523</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934433</v>
+        <v>119934147</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>96891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
         <v>727372</v>
       </c>
       <c r="R5" t="n">
-        <v>7214503</v>
+        <v>7214502</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934147</v>
+        <v>119934345</v>
       </c>
       <c r="B6" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727372</v>
+        <v>727354</v>
       </c>
       <c r="R6" t="n">
-        <v>7214502</v>
+        <v>7214484</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934431</v>
+        <v>119934146</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>96891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727364</v>
+        <v>727338</v>
       </c>
       <c r="R7" t="n">
-        <v>7214523</v>
+        <v>7214647</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934231</v>
+        <v>119934433</v>
       </c>
       <c r="B8" t="n">
-        <v>89269</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727355</v>
+        <v>727372</v>
       </c>
       <c r="R8" t="n">
-        <v>7214538</v>
+        <v>7214503</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934231</v>
+        <v>119934147</v>
       </c>
       <c r="B2" t="n">
-        <v>89269</v>
+        <v>96891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727355</v>
+        <v>727372</v>
       </c>
       <c r="R2" t="n">
-        <v>7214538</v>
+        <v>7214502</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934344</v>
+        <v>119934345</v>
       </c>
       <c r="B3" t="n">
         <v>91858</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727339</v>
+        <v>727354</v>
       </c>
       <c r="R3" t="n">
-        <v>7214582</v>
+        <v>7214484</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934431</v>
+        <v>119934344</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727364</v>
+        <v>727339</v>
       </c>
       <c r="R4" t="n">
-        <v>7214523</v>
+        <v>7214582</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934147</v>
+        <v>119934431</v>
       </c>
       <c r="B5" t="n">
-        <v>96891</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727372</v>
+        <v>727364</v>
       </c>
       <c r="R5" t="n">
-        <v>7214502</v>
+        <v>7214523</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934345</v>
+        <v>119934231</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727354</v>
+        <v>727355</v>
       </c>
       <c r="R6" t="n">
-        <v>7214484</v>
+        <v>7214538</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934146</v>
+        <v>119934433</v>
       </c>
       <c r="B7" t="n">
-        <v>96891</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727338</v>
+        <v>727372</v>
       </c>
       <c r="R7" t="n">
-        <v>7214647</v>
+        <v>7214503</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934433</v>
+        <v>119934146</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>96891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727372</v>
+        <v>727338</v>
       </c>
       <c r="R8" t="n">
-        <v>7214503</v>
+        <v>7214647</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934147</v>
+        <v>119934231</v>
       </c>
       <c r="B2" t="n">
-        <v>96891</v>
+        <v>89269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727372</v>
+        <v>727355</v>
       </c>
       <c r="R2" t="n">
-        <v>7214502</v>
+        <v>7214538</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934231</v>
+        <v>119934433</v>
       </c>
       <c r="B6" t="n">
-        <v>89269</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727355</v>
+        <v>727372</v>
       </c>
       <c r="R6" t="n">
-        <v>7214538</v>
+        <v>7214503</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934433</v>
+        <v>119934147</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>96891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,7 +1278,7 @@
         <v>727372</v>
       </c>
       <c r="R7" t="n">
-        <v>7214503</v>
+        <v>7214502</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934231</v>
+        <v>119934433</v>
       </c>
       <c r="B2" t="n">
-        <v>89269</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727355</v>
+        <v>727372</v>
       </c>
       <c r="R2" t="n">
-        <v>7214538</v>
+        <v>7214503</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934345</v>
+        <v>119934146</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727354</v>
+        <v>727338</v>
       </c>
       <c r="R3" t="n">
-        <v>7214484</v>
+        <v>7214647</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934344</v>
+        <v>119934231</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727339</v>
+        <v>727355</v>
       </c>
       <c r="R4" t="n">
-        <v>7214582</v>
+        <v>7214538</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934431</v>
+        <v>119934344</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727364</v>
+        <v>727339</v>
       </c>
       <c r="R5" t="n">
-        <v>7214523</v>
+        <v>7214582</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934433</v>
+        <v>119934345</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727372</v>
+        <v>727354</v>
       </c>
       <c r="R6" t="n">
-        <v>7214503</v>
+        <v>7214484</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934146</v>
+        <v>119934431</v>
       </c>
       <c r="B8" t="n">
-        <v>96891</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727338</v>
+        <v>727364</v>
       </c>
       <c r="R8" t="n">
-        <v>7214647</v>
+        <v>7214523</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32387-2024 artfynd.xlsx
+++ b/artfynd/A 32387-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934433</v>
+        <v>119934431</v>
       </c>
       <c r="B2" t="n">
         <v>91852</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727372</v>
+        <v>727364</v>
       </c>
       <c r="R2" t="n">
-        <v>7214503</v>
+        <v>7214523</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934146</v>
+        <v>119934147</v>
       </c>
       <c r="B3" t="n">
         <v>96891</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727338</v>
+        <v>727372</v>
       </c>
       <c r="R3" t="n">
-        <v>7214647</v>
+        <v>7214502</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934231</v>
+        <v>119934345</v>
       </c>
       <c r="B4" t="n">
-        <v>89269</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727355</v>
+        <v>727354</v>
       </c>
       <c r="R4" t="n">
-        <v>7214538</v>
+        <v>7214484</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934344</v>
+        <v>119934231</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727339</v>
+        <v>727355</v>
       </c>
       <c r="R5" t="n">
-        <v>7214582</v>
+        <v>7214538</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934345</v>
+        <v>119934433</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727354</v>
+        <v>727372</v>
       </c>
       <c r="R6" t="n">
-        <v>7214484</v>
+        <v>7214503</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119934147</v>
+        <v>119934146</v>
       </c>
       <c r="B7" t="n">
         <v>96891</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>727372</v>
+        <v>727338</v>
       </c>
       <c r="R7" t="n">
-        <v>7214502</v>
+        <v>7214647</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934431</v>
+        <v>119934344</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727364</v>
+        <v>727339</v>
       </c>
       <c r="R8" t="n">
-        <v>7214523</v>
+        <v>7214582</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
